--- a/Server/Common/GameDatasheet/Original_Equipment.xlsx
+++ b/Server/Common/GameDatasheet/Original_Equipment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970461A9-724C-4C0A-A016-8A4908E562CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B6FD2E-59F2-4787-A07E-06C8047FCD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -33,18 +33,6 @@
     <t>sell_price</t>
   </si>
   <si>
-    <t>base_attack</t>
-  </si>
-  <si>
-    <t>base_magic_attack</t>
-  </si>
-  <si>
-    <t>hp_bonus</t>
-  </si>
-  <si>
-    <t>mp_bonus</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -68,14 +56,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp_restore</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mp_restore</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>"초보자의 두건"</t>
   </si>
   <si>
@@ -331,10 +311,6 @@
     <t>"FALSE"</t>
   </si>
   <si>
-    <t>equipment_slot_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>template_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -458,6 +434,34 @@
   </si>
   <si>
     <t>"보석으로 장식된 화려한 검. 세게 휘두르면 나무도 자를 수 있다."</t>
+  </si>
+  <si>
+    <t>physical_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>magical_attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_regenerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mp_regenerate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -828,124 +832,123 @@
     <col min="2" max="2" width="17.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.59765625" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.69921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="73.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="73.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="O1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
       <c r="P1" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="Q1" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Q2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.4">
@@ -953,54 +956,51 @@
         <v>1000</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3">
+        <f>F3*0.1</f>
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>100</v>
       </c>
-      <c r="H3">
-        <f>G3*0.1</f>
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>100</v>
+        <f t="shared" ref="K3:K38" si="0">J3*0.5</f>
+        <v>50</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L38" si="0">K3*0.5</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
-      <c r="N3">
-        <v>0</v>
+      <c r="N3" t="s">
+        <v>90</v>
       </c>
       <c r="O3" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="P3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.4">
@@ -1008,54 +1008,51 @@
         <v>1001</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E4">
-        <v>10001</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
+        <f t="shared" ref="G4:G38" si="1">F4*0.1</f>
+        <v>10</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>200</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H38" si="1">G4*0.1</f>
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>200</v>
-      </c>
       <c r="L4">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
-      <c r="N4">
-        <v>0</v>
+      <c r="N4" t="s">
+        <v>90</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="P4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.4">
@@ -1063,54 +1060,51 @@
         <v>1002</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E5">
-        <v>10002</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>200</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="H5">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>200</v>
-      </c>
       <c r="L5">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
-      <c r="N5">
-        <v>0</v>
+      <c r="N5" t="s">
+        <v>90</v>
       </c>
       <c r="O5" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" t="s">
         <v>96</v>
-      </c>
-      <c r="P5" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.4">
@@ -1118,54 +1112,51 @@
         <v>1003</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E6">
-        <v>10003</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
         <v>100</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
       <c r="K6">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
-      <c r="N6">
-        <v>0</v>
+      <c r="N6" t="s">
+        <v>90</v>
       </c>
       <c r="O6" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="P6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.4">
@@ -1173,54 +1164,51 @@
         <v>1004</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E7">
-        <v>10004</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
         <v>100</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
       <c r="K7">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
-      <c r="N7">
-        <v>0</v>
+      <c r="N7" t="s">
+        <v>90</v>
       </c>
       <c r="O7" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="P7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.4">
@@ -1228,54 +1216,51 @@
         <v>1005</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
         <v>91</v>
       </c>
-      <c r="E8">
-        <v>10005</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
       <c r="O8" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="P8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.4">
@@ -1283,54 +1268,51 @@
         <v>1006</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E9">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="H9">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>200</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>200</v>
-      </c>
       <c r="L9">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" t="s">
+        <v>50</v>
+      </c>
+      <c r="P9" t="s">
         <v>100</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>96</v>
-      </c>
-      <c r="P9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.4">
@@ -1338,54 +1320,51 @@
         <v>1007</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E10">
-        <v>10001</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="H10">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K10">
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="L10">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
-      <c r="N10">
-        <v>0</v>
+      <c r="N10" t="s">
+        <v>90</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="P10" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.4">
@@ -1393,54 +1372,51 @@
         <v>1008</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E11">
-        <v>10002</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="H11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K11">
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="L11">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11">
-        <v>0</v>
+      <c r="N11" t="s">
+        <v>90</v>
       </c>
       <c r="O11" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="P11" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.4">
@@ -1448,54 +1424,51 @@
         <v>1009</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E12">
-        <v>10003</v>
+        <v>10</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="H12">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>200</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>200</v>
-      </c>
       <c r="L12">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12">
-        <v>0</v>
+      <c r="N12" t="s">
+        <v>90</v>
       </c>
       <c r="O12" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="P12" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.4">
@@ -1503,54 +1476,51 @@
         <v>1010</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E13">
-        <v>10004</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="H13">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>200</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>200</v>
-      </c>
       <c r="L13">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>0</v>
       </c>
-      <c r="N13">
-        <v>0</v>
+      <c r="N13" t="s">
+        <v>90</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="P13" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.4">
@@ -1558,54 +1528,51 @@
         <v>1011</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E14">
-        <v>10005</v>
+        <v>10</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="G14">
-        <v>2000</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="H14">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="I14">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L14">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
-      <c r="N14">
-        <v>0</v>
+      <c r="N14" t="s">
+        <v>90</v>
       </c>
       <c r="O14" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="P14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.4">
@@ -1613,54 +1580,51 @@
         <v>1012</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E15">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="G15">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>300</v>
       </c>
       <c r="H15">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K15">
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="L15">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
-      <c r="N15">
-        <v>0</v>
+      <c r="N15" t="s">
+        <v>90</v>
       </c>
       <c r="O15" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="P15" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.4">
@@ -1668,1268 +1632,1200 @@
         <v>1013</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E16">
-        <v>10001</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="G16">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>300</v>
       </c>
       <c r="H16">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K16">
-        <v>800</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="L16">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
-      <c r="N16">
-        <v>0</v>
+      <c r="N16" t="s">
+        <v>90</v>
       </c>
       <c r="O16" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="P16" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1014</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E17">
-        <v>10002</v>
+        <v>20</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="G17">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>300</v>
       </c>
       <c r="H17">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K17">
-        <v>800</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="L17">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
-      <c r="N17">
-        <v>0</v>
+      <c r="N17" t="s">
+        <v>90</v>
       </c>
       <c r="O17" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="P17" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1015</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>10003</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="G18">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>300</v>
       </c>
       <c r="H18">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K18">
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="L18">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="N18">
-        <v>0</v>
+      <c r="N18" t="s">
+        <v>90</v>
       </c>
       <c r="O18" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="P18" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1016</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E19">
-        <v>10004</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>20</v>
+        <v>3000</v>
       </c>
       <c r="G19">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>300</v>
       </c>
       <c r="H19">
-        <f t="shared" si="1"/>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K19">
-        <v>400</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="L19">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19">
-        <v>0</v>
+      <c r="N19" t="s">
+        <v>90</v>
       </c>
       <c r="O19" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="P19" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1017</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E20">
-        <v>10005</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>5000</v>
       </c>
       <c r="G20">
-        <v>5000</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="H20">
-        <f t="shared" si="1"/>
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="I20">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L20">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="N20">
-        <v>0</v>
+      <c r="N20" t="s">
+        <v>90</v>
       </c>
       <c r="O20" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="P20" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>1018</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E21">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>8000</v>
       </c>
       <c r="G21">
-        <v>8000</v>
+        <f t="shared" si="1"/>
+        <v>800</v>
       </c>
       <c r="H21">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>800</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
       <c r="K21">
-        <v>800</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="N21">
-        <v>0</v>
+      <c r="N21" t="s">
+        <v>90</v>
       </c>
       <c r="O21" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="P21" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1019</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E22">
-        <v>10001</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>8000</v>
       </c>
       <c r="G22">
-        <v>8000</v>
+        <f t="shared" si="1"/>
+        <v>800</v>
       </c>
       <c r="H22">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1600</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>1600</v>
-      </c>
       <c r="L22">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
-      <c r="N22">
-        <v>0</v>
+      <c r="N22" t="s">
+        <v>90</v>
       </c>
       <c r="O22" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="P22" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1020</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E23">
-        <v>10002</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>8000</v>
       </c>
       <c r="G23">
-        <v>8000</v>
+        <f t="shared" si="1"/>
+        <v>800</v>
       </c>
       <c r="H23">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1600</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>1600</v>
-      </c>
       <c r="L23">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
-      <c r="N23">
-        <v>0</v>
+      <c r="N23" t="s">
+        <v>90</v>
       </c>
       <c r="O23" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="P23" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E24">
-        <v>10003</v>
+        <v>30</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>8000</v>
       </c>
       <c r="G24">
-        <v>8000</v>
+        <f t="shared" si="1"/>
+        <v>800</v>
       </c>
       <c r="H24">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
         <v>800</v>
       </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
       <c r="K24">
-        <v>800</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="L24">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <v>0</v>
+      <c r="N24" t="s">
+        <v>90</v>
       </c>
       <c r="O24" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="P24" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1022</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E25">
-        <v>10004</v>
+        <v>30</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>8000</v>
       </c>
       <c r="G25">
-        <v>8000</v>
+        <f t="shared" si="1"/>
+        <v>800</v>
       </c>
       <c r="H25">
-        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>800</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
       <c r="K25">
-        <v>800</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="L25">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="N25">
-        <v>0</v>
+      <c r="N25" t="s">
+        <v>90</v>
       </c>
       <c r="O25" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="P25" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1023</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E26">
-        <v>10005</v>
+        <v>30</v>
       </c>
       <c r="F26">
-        <v>30</v>
+        <v>15000</v>
       </c>
       <c r="G26">
-        <v>15000</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
       <c r="H26">
-        <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>120</v>
       </c>
       <c r="I26">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L26">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26">
-        <v>0</v>
+      <c r="N26" t="s">
+        <v>90</v>
       </c>
       <c r="O26" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="P26" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>1024</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E27">
-        <v>10000</v>
+        <v>40</v>
       </c>
       <c r="F27">
-        <v>40</v>
+        <v>12000</v>
       </c>
       <c r="G27">
-        <v>12000</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
       <c r="H27">
-        <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K27">
-        <v>1600</v>
+        <f t="shared" si="0"/>
+        <v>800</v>
       </c>
       <c r="L27">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="N27">
-        <v>0</v>
+      <c r="N27" t="s">
+        <v>90</v>
       </c>
       <c r="O27" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="P27" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>1025</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E28">
-        <v>10001</v>
+        <v>40</v>
       </c>
       <c r="F28">
-        <v>40</v>
+        <v>12000</v>
       </c>
       <c r="G28">
-        <v>12000</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
       <c r="H28">
-        <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="K28">
-        <v>3200</v>
+        <f t="shared" si="0"/>
+        <v>1600</v>
       </c>
       <c r="L28">
-        <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
-      <c r="N28">
-        <v>0</v>
+      <c r="N28" t="s">
+        <v>90</v>
       </c>
       <c r="O28" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="P28" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>1026</v>
       </c>
       <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29">
         <v>40</v>
       </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29">
-        <v>10002</v>
-      </c>
       <c r="F29">
-        <v>40</v>
+        <v>12000</v>
       </c>
       <c r="G29">
-        <v>12000</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
       <c r="H29">
-        <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="K29">
-        <v>3200</v>
+        <f t="shared" si="0"/>
+        <v>1600</v>
       </c>
       <c r="L29">
-        <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29">
-        <v>0</v>
+      <c r="N29" t="s">
+        <v>90</v>
       </c>
       <c r="O29" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="P29" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1027</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E30">
-        <v>10003</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>12000</v>
       </c>
       <c r="G30">
-        <v>12000</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
       <c r="H30">
-        <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K30">
-        <v>1600</v>
+        <f t="shared" si="0"/>
+        <v>800</v>
       </c>
       <c r="L30">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
-      <c r="N30">
-        <v>0</v>
+      <c r="N30" t="s">
+        <v>90</v>
       </c>
       <c r="O30" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="P30" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>1028</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E31">
-        <v>10004</v>
+        <v>40</v>
       </c>
       <c r="F31">
-        <v>40</v>
+        <v>12000</v>
       </c>
       <c r="G31">
-        <v>12000</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
       <c r="H31">
-        <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K31">
-        <v>1600</v>
+        <f t="shared" si="0"/>
+        <v>800</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31">
-        <v>0</v>
+      <c r="N31" t="s">
+        <v>90</v>
       </c>
       <c r="O31" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="P31" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>1029</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E32">
-        <v>10005</v>
+        <v>40</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>20000</v>
       </c>
       <c r="G32">
-        <v>20000</v>
+        <f t="shared" si="1"/>
+        <v>2000</v>
       </c>
       <c r="H32">
-        <f t="shared" si="1"/>
-        <v>2000</v>
+        <v>180</v>
       </c>
       <c r="I32">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L32">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
-      <c r="N32">
-        <v>0</v>
+      <c r="N32" t="s">
+        <v>90</v>
       </c>
       <c r="O32" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="P32" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>1030</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E33">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="F33">
-        <v>50</v>
+        <v>35000</v>
       </c>
       <c r="G33">
-        <v>35000</v>
+        <f t="shared" si="1"/>
+        <v>3500</v>
       </c>
       <c r="H33">
-        <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K33">
-        <v>4000</v>
+        <f t="shared" si="0"/>
+        <v>2000</v>
       </c>
       <c r="L33">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M33">
         <v>0</v>
       </c>
-      <c r="N33">
-        <v>0</v>
+      <c r="N33" t="s">
+        <v>90</v>
       </c>
       <c r="O33" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="P33" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>1031</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E34">
-        <v>10001</v>
+        <v>50</v>
       </c>
       <c r="F34">
-        <v>50</v>
+        <v>35000</v>
       </c>
       <c r="G34">
-        <v>35000</v>
+        <f t="shared" si="1"/>
+        <v>3500</v>
       </c>
       <c r="H34">
-        <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K34">
-        <v>8000</v>
+        <f t="shared" si="0"/>
+        <v>4000</v>
       </c>
       <c r="L34">
-        <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
-      <c r="N34">
-        <v>0</v>
+      <c r="N34" t="s">
+        <v>90</v>
       </c>
       <c r="O34" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="P34" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>1032</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E35">
-        <v>10002</v>
+        <v>50</v>
       </c>
       <c r="F35">
-        <v>50</v>
+        <v>35000</v>
       </c>
       <c r="G35">
-        <v>35000</v>
+        <f t="shared" si="1"/>
+        <v>3500</v>
       </c>
       <c r="H35">
-        <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="K35">
-        <v>8000</v>
+        <f t="shared" si="0"/>
+        <v>4000</v>
       </c>
       <c r="L35">
-        <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
-      <c r="N35">
-        <v>0</v>
+      <c r="N35" t="s">
+        <v>90</v>
       </c>
       <c r="O35" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="P35" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1033</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E36">
-        <v>10003</v>
+        <v>50</v>
       </c>
       <c r="F36">
-        <v>50</v>
+        <v>35000</v>
       </c>
       <c r="G36">
-        <v>35000</v>
+        <f t="shared" si="1"/>
+        <v>3500</v>
       </c>
       <c r="H36">
-        <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K36">
-        <v>4000</v>
+        <f t="shared" si="0"/>
+        <v>2000</v>
       </c>
       <c r="L36">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
-      <c r="N36">
-        <v>0</v>
+      <c r="N36" t="s">
+        <v>90</v>
       </c>
       <c r="O36" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="P36" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>1034</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E37">
-        <v>10004</v>
+        <v>50</v>
       </c>
       <c r="F37">
-        <v>50</v>
+        <v>35000</v>
       </c>
       <c r="G37">
-        <v>35000</v>
+        <f t="shared" si="1"/>
+        <v>3500</v>
       </c>
       <c r="H37">
-        <f t="shared" si="1"/>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K37">
-        <v>4000</v>
+        <f t="shared" si="0"/>
+        <v>2000</v>
       </c>
       <c r="L37">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
-      <c r="N37">
-        <v>0</v>
+      <c r="N37" t="s">
+        <v>90</v>
       </c>
       <c r="O37" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="P37" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>1035</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E38">
-        <v>10005</v>
+        <v>50</v>
       </c>
       <c r="F38">
-        <v>50</v>
+        <v>80000</v>
       </c>
       <c r="G38">
-        <v>80000</v>
+        <f t="shared" si="1"/>
+        <v>8000</v>
       </c>
       <c r="H38">
-        <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>300</v>
       </c>
       <c r="I38">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L38">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
-      <c r="N38">
-        <v>0</v>
+      <c r="N38" t="s">
+        <v>90</v>
       </c>
       <c r="O38" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="P38" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>